--- a/data/availability/projects/mountain-view/mountain-view-ras-el-hekma.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-ras-el-hekma.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for Mountain View Ras El Hekma</t>
+          <t>Live inventory for mountain-view-ras-el-hekma</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,256 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>155</v>
+      </c>
+      <c r="F2" t="n">
+        <v>155</v>
+      </c>
+      <c r="G2" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39.34</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Crete-Twin House-TW-Sep 2025</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>92</v>
+      </c>
+      <c r="F3" t="n">
+        <v>92</v>
+      </c>
+      <c r="G3" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="H3" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Evia-GF-2BR-Apr 2026</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>170</v>
+      </c>
+      <c r="F4" t="n">
+        <v>170</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="H4" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Evia-THL-TH-M-Apr 2026</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>225</v>
+      </c>
+      <c r="F5" t="n">
+        <v>225</v>
+      </c>
+      <c r="G5" t="n">
+        <v>54.57</v>
+      </c>
+      <c r="H5" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>R&amp;T-Villa-SA Feb 2026</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>154</v>
+      </c>
+      <c r="F6" t="n">
+        <v>154</v>
+      </c>
+      <c r="G6" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>R&amp;T-Twin House-TW Feb 2026</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
         </is>
       </c>
     </row>
@@ -557,7 +807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -627,6 +877,1019 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CR-TW-096-B-GF</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Crete-Twin House-TW-Sep 2025</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>155</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Garden: 141.59 sqm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>39341656</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Chalet</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EV-CN4-029-A-GF</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Evia-GF-2BR-Apr 2026</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>92</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Garden: 185.96 sqm</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>18688128</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EV-THL5-081-D-GF</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Evia-THL-TH-M-Apr 2026</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>170</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Garden: 66.43 sqm</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>25315157</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EV-THL5-090-D-GF</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Evia-THL-TH-M-Apr 2026</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>170</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Garden: 66.45 sqm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>25622781</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EV-THL8-080-B-GF</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Evia-THL-TH-M-Apr 2026</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>170</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Garden: 66.97 sqm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>25429314</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EV-THL8-080-F-GF</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Evia-THL-TH-M-Apr 2026</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>170</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Garden: 66.54 sqm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>25419949</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EV-THL8-080-G-GF</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Evia-THL-TH-M-Apr 2026</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>170</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Garden: 66.94 sqm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>25428661</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EV-THL8-089-D-GF</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Evia-THL-TH-M-Apr 2026</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>170</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Garden: 66.52 sqm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>25419513</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EV-THL8-089-E-GF</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Evia-THL-TH-M-Apr 2026</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>170</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Garden: 66.36 sqm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>25211238</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EV-THL8-089-G-GF</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Evia-THL-TH-M-Apr 2026</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>170</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Garden: 66.61 sqm</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>25216680</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Townhouse</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EV-THL8-131-G-GF</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Evia-THL-TH-M-Apr 2026</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>170</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Garden: 81.72 sqm</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>26365298</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>RL-SA-065-1-GF</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>R&amp;T-Villa-SA Feb 2026</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>225</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>62108018</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RL-SA-069-C-GF</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>R&amp;T-Villa-SA Feb 2026</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>225</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>58219581</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>RL-SA-070-A-GF</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>R&amp;T-Villa-SA Feb 2026</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>225</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>58931675</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RL-SA-070-B-GF</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>R&amp;T-Villa-SA Feb 2026</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>225</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>54567498</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RL-SA-070-C-GF</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>R&amp;T-Villa-SA Feb 2026</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>225</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>56722932</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Twin House</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TN-TW-096-B-GF</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>R&amp;T-Twin House-TW Feb 2026</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>154</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>36600413</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>10% down payment over 9 years equal installments</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/availability/projects/mountain-view/mountain-view-ras-el-hekma.xlsx
+++ b/data/availability/projects/mountain-view/mountain-view-ras-el-hekma.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for mountain-view-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -554,7 +564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -587,7 +597,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -604,7 +614,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -735,7 +745,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -759,7 +769,6 @@
       <c r="G2" t="n">
         <v>66.43000000000001</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -770,7 +779,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -792,7 +801,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -816,7 +825,6 @@
       <c r="G3" t="n">
         <v>66.45</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -827,7 +835,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -849,7 +857,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -873,7 +881,6 @@
       <c r="G4" t="n">
         <v>66.97</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -884,7 +891,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -906,7 +913,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -930,7 +937,6 @@
       <c r="G5" t="n">
         <v>66.54000000000001</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -941,7 +947,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -963,7 +969,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -987,7 +993,6 @@
       <c r="G6" t="n">
         <v>66.94</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -998,7 +1003,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1020,7 +1025,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1044,7 +1049,6 @@
       <c r="G7" t="n">
         <v>66.52</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1055,7 +1059,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1077,7 +1081,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1101,7 +1105,6 @@
       <c r="G8" t="n">
         <v>66.36</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1112,7 +1115,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1134,7 +1137,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1158,7 +1161,6 @@
       <c r="G9" t="n">
         <v>66.61</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1169,7 +1171,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1191,7 +1193,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1215,7 +1217,6 @@
       <c r="G10" t="n">
         <v>62.9</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1226,7 +1227,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1248,7 +1249,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1272,7 +1273,6 @@
       <c r="G11" t="n">
         <v>81.72</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>OFF PLAN - 3</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1329,7 +1329,6 @@
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1362,7 +1361,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1386,7 +1385,6 @@
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1419,7 +1417,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1443,7 +1441,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1476,7 +1473,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1500,7 +1497,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
